--- a/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Naming & Trademark Research.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Naming & Trademark Research.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
   <si>
     <t xml:space="preserve">Naming &amp; Trademark Research — búsqueda PRELIMINAR (no es informe de registrabilidad)</t>
   </si>
@@ -68,6 +68,18 @@
     <t xml:space="preserve">Estado</t>
   </si>
   <si>
+    <t xml:space="preserve">ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre del torcedor que participa en el proyecto: autenticidad real, firma como logotipo; requiere consentimiento escrito y licencia de nombre/imagen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninguna marca de puros hallada; posible asociación con Arnaldo Vichot (ex maestro ligador de Partagás, †2026); marca de tabaco similar ARLONDO (Gryson)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECCIONADO por el promotor — condicionado</t>
+  </si>
+  <si>
     <t xml:space="preserve">FOLIO</t>
   </si>
   <si>
@@ -77,7 +89,7 @@
     <t xml:space="preserve">Ninguna hallada en web (S—búsqueda 'Folio cigar')</t>
   </si>
   <si>
-    <t xml:space="preserve">FINALISTA — SELECCIONADO</t>
+    <t xml:space="preserve">FINALISTA — reserva 1</t>
   </si>
   <si>
     <t xml:space="preserve">LUMBRE</t>
@@ -89,7 +101,7 @@
     <t xml:space="preserve">Ninguna hallada</t>
   </si>
   <si>
-    <t xml:space="preserve">FINALISTA — reserva 1</t>
+    <t xml:space="preserve">FINALISTA — reserva 2</t>
   </si>
   <si>
     <t xml:space="preserve">VELADA</t>
@@ -98,7 +110,7 @@
     <t xml:space="preserve">Reunión nocturna; ritual de sobremesa.</t>
   </si>
   <si>
-    <t xml:space="preserve">FINALISTA — reserva 2</t>
+    <t xml:space="preserve">Finalista descartado</t>
   </si>
   <si>
     <t xml:space="preserve">VERSO</t>
@@ -305,13 +317,22 @@
     <t xml:space="preserve">EUIPO (clase 34, 35)</t>
   </si>
   <si>
+    <t xml:space="preserve">Idéntica y similar (ARNALDO, ARNALDO + apellido, ARLONDO, ARNAUD…) + firma como marca figurativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENDIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agente de marcas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OEPM / OCPI / WIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacional, Cuba (vía agente) e internacional; consentimiento de Arnaldo adjunto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Búsqueda idéntica y similar (FOLIO, FOLIUM, PHOLIO) + TMview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENDIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente de marcas</t>
   </si>
   <si>
     <t xml:space="preserve">OEPM (clase 34)</t>
@@ -831,7 +852,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -916,7 +937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -924,7 +945,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>5</v>
@@ -936,7 +957,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>4</v>
@@ -946,7 +967,7 @@
       </c>
       <c r="J5" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C5:I5)</f>
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>17</v>
@@ -955,7 +976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>19</v>
       </c>
@@ -966,16 +987,16 @@
         <v>4</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>4</v>
@@ -985,7 +1006,7 @@
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C6:I6)</f>
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
@@ -1002,13 +1023,13 @@
         <v>24</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>4</v>
@@ -1020,25 +1041,25 @@
         <v>4</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C7:I7)</f>
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>3</v>
@@ -1047,10 +1068,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>4</v>
@@ -1059,53 +1080,53 @@
         <v>4</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C8:I8)</f>
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="F9" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>5</v>
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C9:I9)</f>
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>32</v>
@@ -1119,7 +1140,7 @@
         <v>34</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
@@ -1141,21 +1162,21 @@
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C10:I10)</f>
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>4</v>
@@ -1164,40 +1185,40 @@
         <v>3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C11:I11)</f>
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -1215,25 +1236,25 @@
         <v>4</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C12:I12)</f>
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>3</v>
@@ -1242,118 +1263,118 @@
         <v>3</v>
       </c>
       <c r="E13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C13:I13)</f>
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C14:I14)</f>
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C15:I15)</f>
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>3</v>
@@ -1362,7 +1383,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>4</v>
@@ -1371,25 +1392,25 @@
         <v>4</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C16:I16)</f>
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>2</v>
@@ -1398,26 +1419,26 @@
         <v>3</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C17:I17)</f>
         <v>3.3</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>57</v>
@@ -1437,10 +1458,10 @@
         <v>3</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>4</v>
@@ -1449,11 +1470,11 @@
         <v>2</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C18:I18)</f>
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>60</v>
@@ -1470,29 +1491,29 @@
         <v>63</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C19:I19)</f>
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>64</v>
@@ -1515,13 +1536,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>1</v>
@@ -1531,12 +1552,12 @@
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C20:I20)</f>
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1548,16 +1569,16 @@
         <v>71</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>4</v>
@@ -1570,7 +1591,7 @@
       </c>
       <c r="J21" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C21:I21)</f>
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>72</v>
@@ -1590,13 +1611,13 @@
         <v>2</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>4</v>
@@ -1609,7 +1630,7 @@
       </c>
       <c r="J22" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C22:I22)</f>
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>76</v>
@@ -1626,29 +1647,29 @@
         <v>79</v>
       </c>
       <c r="C23" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C23:I23)</f>
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>80</v>
@@ -1690,49 +1711,88 @@
         <v>2.35</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I25" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C25:I25)</f>
+        <v>2.35</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <f aca="false">SUMPRODUCT($C$3:$I$3,C26:I26)</f>
         <v>2.15</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>87</v>
+      <c r="K26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1763,12 +1823,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1776,33 +1836,33 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1810,67 +1870,67 @@
         <v>15</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1878,38 +1938,72 @@
         <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>111</v>
+      <c r="B12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>

--- a/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Naming & Trademark Research.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Naming & Trademark Research.xlsx
@@ -68,13 +68,13 @@
     <t xml:space="preserve">Estado</t>
   </si>
   <si>
-    <t xml:space="preserve">ARNALDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre del torcedor que participa en el proyecto: autenticidad real, firma como logotipo; requiere consentimiento escrito y licencia de nombre/imagen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninguna marca de puros hallada; posible asociación con Arnaldo Vichot (ex maestro ligador de Partagás, †2026); marca de tabaco similar ARLONDO (Gryson)</t>
+    <t xml:space="preserve">ARNALDO VALLÉS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre y apellido del torcedor que participa en el proyecto (rebranding 17/10/2026): autenticidad real, firma como logotipo; requiere consentimiento escrito y licencia de nombre/imagen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninguna marca de puros «Arnaldo Vallés» hallada; DON VALLES (EE. UU., puros, 2016) y ARLONDO (Gryson, tabaco) a analizar; el apellido atenúa la asociación con Arnaldo Vichot (ex maestro ligador de Partagás, †2026)</t>
   </si>
   <si>
     <t xml:space="preserve">SELECCIONADO por el promotor — condicionado</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">EUIPO (clase 34, 35)</t>
   </si>
   <si>
-    <t xml:space="preserve">Idéntica y similar (ARNALDO, ARNALDO + apellido, ARLONDO, ARNAUD…) + firma como marca figurativa</t>
+    <t xml:space="preserve">Idéntica y similar (ARNALDO VALLÉS, ARNALDO, VALLÉS, DON VALLES, ARLONDO, ARNAUD…) + firma como marca figurativa</t>
   </si>
   <si>
     <t xml:space="preserve">PENDIENTE</t>
@@ -937,7 +937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -945,13 +945,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="J5" s="9" t="n">
         <f aca="false">SUMPRODUCT($C$3:$I$3,C5:I5)</f>
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>17</v>
